--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_290626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_290626.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A49EA-6D3D-42BC-94CA-278BDD10DC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3194CC8C-942A-4A89-9126-772889CDD997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -692,6 +692,15 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,15 +757,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1185,66 +1185,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="54"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="57"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="55" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="56"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="55" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="56"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="57" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="57"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1497,14 +1497,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="38" customWidth="1"/>
-    <col min="2" max="2" width="25" style="60" customWidth="1"/>
+    <col min="2" max="2" width="25" style="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="40" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="42" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       <c r="A3" s="36">
         <v>2</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="42" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       <c r="A4" s="36">
         <v>3</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="42" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       <c r="A5" s="36">
         <v>4</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="42" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       <c r="A6" s="36">
         <v>5</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="42" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       <c r="A7" s="36">
         <v>6</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="42" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       <c r="A8" s="36">
         <v>7</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="42" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
       <c r="A9" s="36">
         <v>8</v>
       </c>
-      <c r="B9" s="61" t="s">
+      <c r="B9" s="42" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       <c r="A10" s="36">
         <v>9</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="42" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       <c r="A11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="42" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       <c r="A12" s="36">
         <v>11</v>
       </c>
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="42" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       <c r="A13" s="36">
         <v>12</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="42" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       <c r="A14" s="36">
         <v>13</v>
       </c>
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="42" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       <c r="A15" s="36">
         <v>14</v>
       </c>
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="42" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       <c r="A16" s="36">
         <v>15</v>
       </c>
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="42" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       <c r="A17" s="36">
         <v>16</v>
       </c>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="42" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       <c r="A18" s="36">
         <v>17</v>
       </c>
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="42" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       <c r="A19" s="36">
         <v>18</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="42" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       <c r="A20" s="36">
         <v>19</v>
       </c>
-      <c r="B20" s="61" t="s">
+      <c r="B20" s="42" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       <c r="A21" s="36">
         <v>20</v>
       </c>
-      <c r="B21" s="61" t="s">
+      <c r="B21" s="42" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       <c r="A22" s="36">
         <v>21</v>
       </c>
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="42" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       <c r="A23" s="36">
         <v>22</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="42" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       <c r="A24" s="36">
         <v>23</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="42" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       <c r="A25" s="36">
         <v>24</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="42" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="A26" s="36">
         <v>25</v>
       </c>
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="42" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       <c r="A27" s="36">
         <v>26</v>
       </c>
-      <c r="B27" s="61" t="s">
+      <c r="B27" s="42" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       <c r="A28" s="36">
         <v>27</v>
       </c>
-      <c r="B28" s="61" t="s">
+      <c r="B28" s="42" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       <c r="A29" s="36">
         <v>28</v>
       </c>
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="42" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       <c r="A30" s="36">
         <v>29</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="42" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       <c r="A31" s="36">
         <v>30</v>
       </c>
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="42" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       <c r="A32" s="36">
         <v>31</v>
       </c>
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="42" t="s">
         <v>61</v>
       </c>
     </row>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_290626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 06/NKSX_VNSH03_290626.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3194CC8C-942A-4A89-9126-772889CDD997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA1C20B-351C-421E-87C4-6F5AFACBCDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
